--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -2099,7 +2099,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2133,7 +2133,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2148,7 +2148,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2178,7 +2178,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2193,7 +2193,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2223,7 +2223,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2253,7 +2253,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2268,7 +2268,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2298,7 +2298,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2328,7 +2328,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2358,7 +2358,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2373,7 +2373,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2388,7 +2388,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2418,7 +2418,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2433,7 +2433,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,7 +2463,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2478,7 +2478,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2508,7 +2508,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2538,7 +2538,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2568,7 +2568,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2583,7 +2583,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2598,7 +2598,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2628,7 +2628,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2658,7 +2658,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2688,7 +2688,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2718,7 +2718,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2748,7 +2748,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2763,7 +2763,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2823,7 +2823,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2838,7 +2838,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2868,7 +2868,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2883,7 +2883,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2913,7 +2913,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2928,7 +2928,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2958,7 +2958,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2973,7 +2973,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2988,7 +2988,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3003,7 +3003,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3018,7 +3018,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3033,7 +3033,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -3063,7 +3063,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3078,7 +3078,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3108,7 +3108,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3123,7 +3123,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3138,7 +3138,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3168,7 +3168,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3599,7 +3599,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3682,16 +3682,21 @@
           <t>ID</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>319.0</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3699,16 +3704,21 @@
           <t>Website</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://esatus.com/en/</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3716,16 +3726,21 @@
           <t>Logo</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Esatus-Logo.png</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3733,16 +3748,21 @@
           <t>Mission Statement</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Enforcing Information Security</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3750,16 +3770,21 @@
           <t>Live Source Mission Statement</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://esatus.com/files/Whitepaper_esatus_SSI_Roll_out_20200224_464a9d566b.pdf</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3767,16 +3792,21 @@
           <t>Archived Source Mission Statement</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20250211204611/https://esatus.com/files/Whitepaper_esatus_SSI_Roll_out_20200224_464a9d566b.pdf</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3784,16 +3814,21 @@
           <t>Project Announcement Date</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3801,16 +3836,21 @@
           <t>Live Source Project Announcement Date</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://twitter.com/esatus_SOWL/status/1230498444541861888</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3818,16 +3858,21 @@
           <t>Archived Source Project Announcement Date</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://archive.ph/avuo5</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3835,16 +3880,21 @@
           <t>Project Launch Date</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3852,16 +3902,21 @@
           <t>Live Source Project Launch Date</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://twitter.com/esatus_SOWL/status/1228409009918574594</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3869,16 +3924,21 @@
           <t>Archived Source Project Launch Date</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://archive.ph/nucvk</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3886,16 +3946,21 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3903,16 +3968,21 @@
           <t>Live Source Status</t>
         </is>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/esatus-wallet/id1496769057</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3920,16 +3990,21 @@
           <t>Archived Source Status</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://archive.ph/5Sdy5</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3937,16 +4012,21 @@
           <t>Politically Involved?</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3954,16 +4034,21 @@
           <t>Live Source Politically Involved</t>
         </is>
       </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://esatus.com/en/</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3971,16 +4056,21 @@
           <t>Archived Source Politically Involved</t>
         </is>
       </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://archive.ph/gXzU6#selection-1081.45-1081.52</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3988,16 +4078,21 @@
           <t>Tech Stack Descriptions</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>The app will use at least one individual connection with a unique decentralized identifier (DID) while communicating with each different agent in a network so that your online activity cannot be tracked. After revealing claims your counterpart can verify the identity of the issuer of the credential, the validity of the credential (i.e. that it is has not been revoked by the issuer) and that the content is trustworthy.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4005,16 +4100,21 @@
           <t>Live Source Tech Stack Description</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/be/app/esatus-wallet/id1496769057</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4022,16 +4122,21 @@
           <t>Archived Source Tech Stack Description</t>
         </is>
       </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://archive.ph/i7QNV</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4039,16 +4144,21 @@
           <t>Public Code Repository</t>
         </is>
       </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://github.com/esatus</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4056,16 +4166,21 @@
           <t>Does it use SSI Technology?</t>
         </is>
       </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4073,16 +4188,21 @@
           <t>Live Source Does it use SSI Technology?</t>
         </is>
       </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://esatus.com/files/esatus_principles_20210713_a62a3df1cd.pdf</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4090,16 +4210,21 @@
           <t>Archived Source Does it use SSI Technology?</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20241226161327/https://esatus.com/files/esatus_principles_20210713_a62a3df1cd.pdf</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4107,16 +4232,21 @@
           <t>Uses/endorses ZKP</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4133,7 +4263,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4141,16 +4271,21 @@
           <t>Archived Source Uses / Endorses ZKP</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Actionlog_Digital_Identity_IAM_for_Applications_with_SSI_20190226_6055b6004a.pdf</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4158,16 +4293,21 @@
           <t>DLT Data Availability</t>
         </is>
       </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Uses DLT, no specifications</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4175,16 +4315,21 @@
           <t>Has Exportable Credentials</t>
         </is>
       </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4201,7 +4346,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4209,16 +4354,21 @@
           <t>Archived Source Has Exportable Credentials</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Export-option.png</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4226,16 +4376,21 @@
           <t>Credential And Key Storage</t>
         </is>
       </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4243,16 +4398,21 @@
           <t>Live Source Credential And Key Storage</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/us/app/esatus-wallet/id1496769057</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4260,16 +4420,21 @@
           <t>Archived Source Credential And Key Storage</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://archive.ph/5Sdy5#selection-2343.81-2437.13</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4277,16 +4442,21 @@
           <t>Targets Holders</t>
         </is>
       </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4303,7 +4473,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4311,16 +4481,21 @@
           <t>Archived Source Targets Holders</t>
         </is>
       </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Users.png</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4328,16 +4503,21 @@
           <t>Targets Issuers</t>
         </is>
       </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4354,7 +4534,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4362,16 +4542,21 @@
           <t>Archived Source Targets Issuers</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Actionlog_Digital_Identity_IAM_for_Applications_with_SSI_20190226_6055b6004a.pdf</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4379,16 +4564,21 @@
           <t>Targets Verifiers</t>
         </is>
       </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4405,7 +4595,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4413,16 +4603,21 @@
           <t>Archived Source Targets Verifiers</t>
         </is>
       </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/Actionlog_Digital_Identity_IAM_for_Applications_with_SSI_20190226_6055b6004a.pdf</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4430,16 +4625,21 @@
           <t>Government relation</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Government of British Columbia</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4447,16 +4647,21 @@
           <t>Government relation Archived Source</t>
         </is>
       </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://archive.ph/QrwGA</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4464,16 +4669,21 @@
           <t>Government relation Live Source</t>
         </is>
       </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/esatussowl_blockchain-wallet-dlt-activity-6650396876644339713-goTU/?trk=public_profile_like_view</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4490,7 +4700,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4507,7 +4717,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4524,7 +4734,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4532,16 +4742,21 @@
           <t>Affiliated Entity / Partner</t>
         </is>
       </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Neosfer GmbH (Neosfer)</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4549,16 +4764,21 @@
           <t>Affiliated Entity / Partner Live Source</t>
         </is>
       </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://archive.ph/SgGF8#selection-1653.0-1657.338</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4566,16 +4786,21 @@
           <t>Affiliated Entity / Partner Archived Source</t>
         </is>
       </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://cheqd.io/blog/cheqd-announces-multiple-partnerships-with-market-leading-self-sovereign-identity-vendors-ahead-of-mainnet-launch/</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4592,7 +4817,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4609,7 +4834,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4626,7 +4851,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4634,16 +4859,21 @@
           <t>Standard/Protocol Used</t>
         </is>
       </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>W3C Verifiable Credentials Data Model</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4651,16 +4881,21 @@
           <t>Standard/Protocol Used Live Source</t>
         </is>
       </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://esatus.com/files/esatus_principles_20210713_a62a3df1cd.pdf</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4668,16 +4903,21 @@
           <t>Standard/Protocol Used Archived Source</t>
         </is>
       </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/20241226161327/https://esatus.com/files/esatus_principles_20210713_a62a3df1cd.pdf</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4685,16 +4925,21 @@
           <t>Blockchains / Verifiable Data Registries</t>
         </is>
       </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IDunion</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4702,16 +4947,21 @@
           <t>Blockchains / Verifiable Data Registries Archived Source</t>
         </is>
       </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://did-map-resources.s3.amazonaws.com/Western+Europe/Esatus/esatus_ledgers.jpeg</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4728,7 +4978,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4736,16 +4986,21 @@
           <t>App Store Link</t>
         </is>
       </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=com.esatus.wallet&amp;hl=en_US</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4753,16 +5008,21 @@
           <t>Regulations Followed</t>
         </is>
       </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EU GDPR - EU General Data Protection Regulation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4770,16 +5030,21 @@
           <t>Regulations Followed Archvied Source</t>
         </is>
       </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://archive.ph/ps0zl#selection-1997.409-1997.473</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4787,16 +5052,21 @@
           <t>Regulations Followed Live Source</t>
         </is>
       </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://esatus.com/en/data-privacy/</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4804,16 +5074,21 @@
           <t>Person of Interest</t>
         </is>
       </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jürgen Eichhöfer</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4821,16 +5096,21 @@
           <t>Person of Interest Work Title</t>
         </is>
       </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4838,16 +5118,21 @@
           <t>Person of Interest Archived Source</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://archive.ph/a9aZC#selection-755.0-864.1</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4855,16 +5140,21 @@
           <t>Person of Interest Live Source</t>
         </is>
       </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://esatus.com/en/about-us/</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4872,16 +5162,21 @@
           <t>Managing Entity</t>
         </is>
       </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>esatus AG (esatus)</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4889,16 +5184,21 @@
           <t>Managing Entity Archived Source</t>
         </is>
       </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://archive.ph/avuo5</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>COOV</t>
+          <t>esatus</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4906,9 +5206,14 @@
           <t>Managing Entity Archived Source.1</t>
         </is>
       </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://twitter.com/esatus_SOWL/status/1230498444541861888</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>⬜️</t>
+          <t>❌</t>
         </is>
       </c>
     </row>
